--- a/data/trans_bre/P2A_ner_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Edad-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,41</t>
+          <t>-0,77; 2,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,08</t>
+          <t>-0,99; 1,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 4,25</t>
+          <t>-0,93; 4,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 4,01</t>
+          <t>-2,34; 3,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,65; 348,31</t>
+          <t>-45,27; 308,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-66,25; 340,81</t>
+          <t>-65,46; 378,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 302,35</t>
+          <t>-32,4; 252,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,59</t>
+          <t>-1,46; 1,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 3,53</t>
+          <t>0,02; 3,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,07</t>
+          <t>-0,76; 3,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,82</t>
+          <t>-2,26; 3,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 111,31</t>
+          <t>-55,26; 120,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 413,41</t>
+          <t>-4,84; 391,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 200,97</t>
+          <t>-26,1; 217,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 253,72</t>
+          <t>-60,41; 288,69</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,56</t>
+          <t>-0,78; 3,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,44</t>
+          <t>-2,29; 2,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,58</t>
+          <t>1,9; 6,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,94</t>
+          <t>-2,89; 1,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 150,83</t>
+          <t>-19,61; 168,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,17; 74,44</t>
+          <t>-41,09; 65,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,74; 240,47</t>
+          <t>36,37; 259,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-60,35; 44,87</t>
+          <t>-58,26; 52,14</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,76</t>
+          <t>0,92; 5,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,78</t>
+          <t>0,08; 4,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 10,23</t>
+          <t>4,01; 10,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,41</t>
+          <t>-0,67; 4,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,85; 404,66</t>
+          <t>23,94; 427,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 255,15</t>
+          <t>-0,06; 261,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,36; 249,65</t>
+          <t>59,65; 255,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 277,55</t>
+          <t>-14,13; 252,79</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 4,44</t>
+          <t>-1,41; 4,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 5,21</t>
+          <t>-0,43; 4,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 16,22</t>
+          <t>7,6; 16,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,75</t>
+          <t>0,19; 4,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 158,89</t>
+          <t>-28,92; 187,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 235,68</t>
+          <t>-13,83; 243,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,37; 308,21</t>
+          <t>81,6; 325,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 156,86</t>
+          <t>0,52; 168,08</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 6,17</t>
+          <t>-0,47; 6,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,61</t>
+          <t>1,32; 9,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,12; 17,25</t>
+          <t>7,71; 16,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 70,3</t>
+          <t>2,28; 68,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 218,74</t>
+          <t>-12,0; 254,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,25; 300,01</t>
+          <t>15,08; 315,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>143,42; 692,49</t>
+          <t>120,75; 664,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60,77; 3108,65</t>
+          <t>59,56; 3949,16</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 7,29</t>
+          <t>-0,49; 7,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 5,17</t>
+          <t>-2,71; 5,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,36; 13,74</t>
+          <t>3,24; 13,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 3,34</t>
+          <t>-2,16; 3,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 415,02</t>
+          <t>-16,95; 356,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 181,04</t>
+          <t>-39,57; 189,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,48; 231,34</t>
+          <t>27,0; 224,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-30,26; 107,28</t>
+          <t>-31,84; 86,14</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,71</t>
+          <t>0,97; 2,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,93</t>
+          <t>0,9; 2,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,18; 7,74</t>
+          <t>5,24; 7,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 23,61</t>
+          <t>0,93; 23,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,12; 112,13</t>
+          <t>29,09; 114,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,38; 109,49</t>
+          <t>25,21; 106,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>102,14; 197,09</t>
+          <t>104,1; 194,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>24,67; 863,0</t>
+          <t>25,51; 828,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>75,73%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,18</t>
+          <t>-0,77; 2,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,92</t>
+          <t>-1,06; 1,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 4,05</t>
+          <t>-0,86; 4,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 3,94</t>
+          <t>-1,65; 3,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,27; 308,92</t>
+          <t>-39,02; 400,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-65,46; 378,8</t>
+          <t>-59,57; 332,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 252,73</t>
+          <t>-33,05; 260,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,8</t>
+          <t>-1,49; 1,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 3,37</t>
+          <t>0,14; 3,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,16</t>
+          <t>-0,83; 3,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,12</t>
+          <t>-1,78; 3,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,26; 120,45</t>
+          <t>-57,5; 102,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 391,14</t>
+          <t>1,43; 397,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,1; 217,93</t>
+          <t>-28,31; 228,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,41; 288,69</t>
+          <t>-48,93; 300,56</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-22,01%</t>
+          <t>-1,19%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,97</t>
+          <t>-1,0; 3,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,27</t>
+          <t>-2,44; 2,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,99</t>
+          <t>1,89; 6,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,09</t>
+          <t>-2,17; 1,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 168,64</t>
+          <t>-26,13; 157,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 65,61</t>
+          <t>-41,25; 65,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,37; 259,5</t>
+          <t>37,61; 249,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,26; 52,14</t>
+          <t>-48,9; 104,3</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,81</t>
+          <t>1,0; 5,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,78</t>
+          <t>-0,09; 4,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 10,14</t>
+          <t>3,8; 10,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,32</t>
+          <t>-1,37; 2,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,94; 427,4</t>
+          <t>24,94; 412,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 261,8</t>
+          <t>-6,45; 232,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,65; 255,4</t>
+          <t>52,32; 241,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 252,79</t>
+          <t>-23,74; 90,02</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>65,46%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 4,88</t>
+          <t>-1,77; 4,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,89</t>
+          <t>-0,24; 5,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,6; 16,22</t>
+          <t>7,41; 16,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,66</t>
+          <t>0,44; 4,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,92; 187,48</t>
+          <t>-30,94; 176,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 243,33</t>
+          <t>-8,34; 246,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,6; 325,95</t>
+          <t>77,92; 304,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 168,08</t>
+          <t>4,48; 163,3</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34,55</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1029,42%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 6,77</t>
+          <t>-0,63; 6,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 9,12</t>
+          <t>1,0; 8,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,71; 16,94</t>
+          <t>7,96; 17,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 68,38</t>
+          <t>0,59; 5,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 254,23</t>
+          <t>-12,17; 231,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,08; 315,83</t>
+          <t>12,66; 305,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>120,75; 664,43</t>
+          <t>132,15; 680,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,56; 3949,16</t>
+          <t>11,43; 227,03</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 7,09</t>
+          <t>-0,5; 7,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 5,27</t>
+          <t>-2,49; 5,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 13,61</t>
+          <t>3,38; 13,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,11</t>
+          <t>-2,73; 2,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 356,39</t>
+          <t>-14,46; 383,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-39,57; 189,4</t>
+          <t>-38,56; 186,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,0; 224,94</t>
+          <t>31,07; 227,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-31,84; 86,14</t>
+          <t>-36,21; 85,09</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,53</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>199,66%</t>
+          <t>39,07%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,8</t>
+          <t>0,94; 2,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,81</t>
+          <t>0,95; 2,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,24; 7,83</t>
+          <t>5,11; 7,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 23,54</t>
+          <t>0,45; 2,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,09; 114,4</t>
+          <t>28,71; 116,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,21; 106,76</t>
+          <t>26,41; 108,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>104,1; 194,76</t>
+          <t>101,07; 195,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>25,51; 828,48</t>
+          <t>11,1; 79,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
